--- a/docs/SJ2022.xlsx
+++ b/docs/SJ2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edilbertosuarez/Documents/Proyectos/icfes/icfes-analyzer/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59E40E-B00A-A84B-B845-719B08BF3CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF2C610-67ED-8344-80A5-0C96DA240978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="219">
   <si>
     <t>Grupo</t>
   </si>
@@ -663,6 +663,36 @@
   </si>
   <si>
     <t>Apellido</t>
+  </si>
+  <si>
+    <t>% LC</t>
+  </si>
+  <si>
+    <t>% MAT</t>
+  </si>
+  <si>
+    <t>% SOC</t>
+  </si>
+  <si>
+    <t>% NAT</t>
+  </si>
+  <si>
+    <t>% ING</t>
+  </si>
+  <si>
+    <t>Nivel LC</t>
+  </si>
+  <si>
+    <t>Nivel MAT</t>
+  </si>
+  <si>
+    <t>Nivel SOC</t>
+  </si>
+  <si>
+    <t>Nivel NAT</t>
+  </si>
+  <si>
+    <t>Nivel ING</t>
   </si>
 </sst>
 </file>
@@ -717,11 +747,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -942,7 +971,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:T126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="37.6640625" customWidth="1"/>
@@ -950,39 +979,69 @@
     <col min="4" max="4" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L1" t="s">
+        <v>210</v>
+      </c>
+      <c r="M1" t="s">
+        <v>211</v>
+      </c>
+      <c r="N1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O1" t="s">
+        <v>213</v>
+      </c>
+      <c r="P1" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>215</v>
+      </c>
+      <c r="R1" t="s">
+        <v>216</v>
+      </c>
+      <c r="S1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,7 +1073,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1046,7 +1105,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1078,7 +1137,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,7 +1169,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1142,7 +1201,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,7 +1233,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,7 +1265,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1238,7 +1297,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1270,7 +1329,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1302,7 +1361,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1334,7 +1393,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -1366,7 +1425,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -1398,7 +1457,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -1430,7 +1489,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>7</v>
       </c>
@@ -4956,7 +5015,7 @@
       <c r="C126" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E126">
